--- a/scripts/create_sheets/output/attendance_D4.xlsx
+++ b/scripts/create_sheets/output/attendance_D4.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -56,12 +59,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -429,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -445,6 +451,7 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,6 +518,11 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Week 10</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Total Attendance</t>
         </is>
       </c>
     </row>
@@ -538,6 +550,10 @@
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
+      <c r="N2" s="3">
+        <f>SUMPRODUCT((UPPER(D2:M2)="P")+(D2:M2="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -563,6 +579,10 @@
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
+      <c r="N3" s="3">
+        <f>SUMPRODUCT((UPPER(D3:M3)="P")+(D3:M3="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -588,6 +608,10 @@
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
+      <c r="N4" s="3">
+        <f>SUMPRODUCT((UPPER(D4:M4)="P")+(D4:M4="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -613,6 +637,10 @@
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
+      <c r="N5" s="3">
+        <f>SUMPRODUCT((UPPER(D5:M5)="P")+(D5:M5="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -638,6 +666,10 @@
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
+      <c r="N6" s="3">
+        <f>SUMPRODUCT((UPPER(D6:M6)="P")+(D6:M6="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -663,6 +695,10 @@
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
+      <c r="N7" s="3">
+        <f>SUMPRODUCT((UPPER(D7:M7)="P")+(D7:M7="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -688,6 +724,10 @@
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
+      <c r="N8" s="3">
+        <f>SUMPRODUCT((UPPER(D8:M8)="P")+(D8:M8="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -713,6 +753,10 @@
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
+      <c r="N9" s="3">
+        <f>SUMPRODUCT((UPPER(D9:M9)="P")+(D9:M9="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -738,6 +782,10 @@
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
+      <c r="N10" s="3">
+        <f>SUMPRODUCT((UPPER(D10:M10)="P")+(D10:M10="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -763,6 +811,10 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
+      <c r="N11" s="3">
+        <f>SUMPRODUCT((UPPER(D11:M11)="P")+(D11:M11="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -788,6 +840,10 @@
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
+      <c r="N12" s="3">
+        <f>SUMPRODUCT((UPPER(D12:M12)="P")+(D12:M12="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -813,6 +869,10 @@
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
+      <c r="N13" s="3">
+        <f>SUMPRODUCT((UPPER(D13:M13)="P")+(D13:M13="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -838,6 +898,10 @@
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
+      <c r="N14" s="3">
+        <f>SUMPRODUCT((UPPER(D14:M14)="P")+(D14:M14="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -863,6 +927,10 @@
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
+      <c r="N15" s="3">
+        <f>SUMPRODUCT((UPPER(D15:M15)="P")+(D15:M15="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -888,6 +956,10 @@
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
+      <c r="N16" s="3">
+        <f>SUMPRODUCT((UPPER(D16:M16)="P")+(D16:M16="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -913,6 +985,10 @@
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
+      <c r="N17" s="3">
+        <f>SUMPRODUCT((UPPER(D17:M17)="P")+(D17:M17="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -938,6 +1014,10 @@
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
+      <c r="N18" s="3">
+        <f>SUMPRODUCT((UPPER(D18:M18)="P")+(D18:M18="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -963,6 +1043,10 @@
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
+      <c r="N19" s="3">
+        <f>SUMPRODUCT((UPPER(D19:M19)="P")+(D19:M19="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -988,6 +1072,10 @@
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
+      <c r="N20" s="3">
+        <f>SUMPRODUCT((UPPER(D20:M20)="P")+(D20:M20="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1013,6 +1101,10 @@
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
+      <c r="N21" s="3">
+        <f>SUMPRODUCT((UPPER(D21:M21)="P")+(D21:M21="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1038,6 +1130,10 @@
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
+      <c r="N22" s="3">
+        <f>SUMPRODUCT((UPPER(D22:M22)="P")+(D22:M22="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1063,6 +1159,10 @@
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
+      <c r="N23" s="3">
+        <f>SUMPRODUCT((UPPER(D23:M23)="P")+(D23:M23="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1088,6 +1188,10 @@
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
+      <c r="N24" s="3">
+        <f>SUMPRODUCT((UPPER(D24:M24)="P")+(D24:M24="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1113,6 +1217,10 @@
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
+      <c r="N25" s="3">
+        <f>SUMPRODUCT((UPPER(D25:M25)="P")+(D25:M25="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1138,6 +1246,10 @@
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
+      <c r="N26" s="3">
+        <f>SUMPRODUCT((UPPER(D26:M26)="P")+(D26:M26="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1163,6 +1275,10 @@
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
+      <c r="N27" s="3">
+        <f>SUMPRODUCT((UPPER(D27:M27)="P")+(D27:M27="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1188,6 +1304,10 @@
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
+      <c r="N28" s="3">
+        <f>SUMPRODUCT((UPPER(D28:M28)="P")+(D28:M28="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1213,6 +1333,10 @@
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
+      <c r="N29" s="3">
+        <f>SUMPRODUCT((UPPER(D29:M29)="P")+(D29:M29="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1238,6 +1362,10 @@
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
+      <c r="N30" s="3">
+        <f>SUMPRODUCT((UPPER(D30:M30)="P")+(D30:M30="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1263,6 +1391,10 @@
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
+      <c r="N31" s="3">
+        <f>SUMPRODUCT((UPPER(D31:M31)="P")+(D31:M31="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1288,6 +1420,10 @@
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
+      <c r="N32" s="3">
+        <f>SUMPRODUCT((UPPER(D32:M32)="P")+(D32:M32="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1313,6 +1449,10 @@
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
+      <c r="N33" s="3">
+        <f>SUMPRODUCT((UPPER(D33:M33)="P")+(D33:M33="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1338,6 +1478,10 @@
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
+      <c r="N34" s="3">
+        <f>SUMPRODUCT((UPPER(D34:M34)="P")+(D34:M34="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1363,6 +1507,10 @@
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
+      <c r="N35" s="3">
+        <f>SUMPRODUCT((UPPER(D35:M35)="P")+(D35:M35="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1388,6 +1536,10 @@
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
+      <c r="N36" s="3">
+        <f>SUMPRODUCT((UPPER(D36:M36)="P")+(D36:M36="1"))</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1413,6 +1565,10 @@
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
+      <c r="N37" s="3">
+        <f>SUMPRODUCT((UPPER(D37:M37)="P")+(D37:M37="1"))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
